--- a/AAII_Financials/Yearly/NUTX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NUTX_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/NUTX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NUTX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>NUTX</t>
   </si>
@@ -656,147 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>247600</v>
+      </c>
+      <c r="E8" s="3">
         <v>219300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>18800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>212900</v>
+      </c>
+      <c r="E9" s="3">
         <v>205800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>14600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>800</v>
       </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
       <c r="I9" s="3">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E10" s="3">
         <v>13500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>500</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
       <c r="I10" s="3">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" s="3">
         <v>500</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,26 +821,27 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="3">
         <v>300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>800</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>5</v>
       </c>
@@ -838,9 +851,12 @@
       <c r="K12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,69 +884,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E14" s="3">
         <v>402000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3">
         <v>700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>200</v>
       </c>
       <c r="G15" s="3">
         <v>200</v>
       </c>
       <c r="H15" s="3">
+        <v>200</v>
+      </c>
+      <c r="I15" s="3">
         <v>700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>500</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -940,68 +965,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>279400</v>
+      </c>
+      <c r="E17" s="3">
         <v>625900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1000</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-406600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1014,140 +1046,153 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1800</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-394000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-500</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E22" s="3">
         <v>12500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>400</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-419600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6000</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-500</v>
       </c>
       <c r="K23" s="3">
         <v>-500</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E24" s="3">
         <v>13100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1000</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,9 +1208,12 @@
       <c r="K24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1193,69 +1241,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-432700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6000</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-500</v>
       </c>
       <c r="K26" s="3">
         <v>-500</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-45800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-424800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6000</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-500</v>
       </c>
       <c r="K27" s="3">
         <v>-500</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1283,39 +1340,45 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>6600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-7000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>600</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1343,9 +1406,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1373,69 +1439,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1800</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-45800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-424800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>100</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1463,74 +1538,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-45800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-424800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>100</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1543,8 +1627,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1557,26 +1642,27 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E41" s="3">
         <v>34300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15300</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
       <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>1100</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
       <c r="I41" s="3">
         <v>0</v>
       </c>
@@ -1584,11 +1670,14 @@
         <v>0</v>
       </c>
       <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1616,27 +1705,30 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E43" s="3">
         <v>58300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2100</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
       <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
       <c r="I43" s="3">
         <v>0</v>
       </c>
@@ -1644,22 +1736,25 @@
         <v>0</v>
       </c>
       <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E44" s="3">
         <v>3500</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G44" s="3">
         <v>0</v>
@@ -1667,86 +1762,95 @@
       <c r="H44" s="3">
         <v>0</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
+      <c r="I44" s="3">
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E45" s="3">
         <v>1900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
         <v>0</v>
       </c>
       <c r="J45" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3">
+        <v>500</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E46" s="3">
         <v>98000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1200</v>
       </c>
-      <c r="H46" s="3">
-        <v>0</v>
-      </c>
       <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
         <v>100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>900</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F47" s="3">
         <v>0</v>
@@ -1766,27 +1870,30 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>269400</v>
+      </c>
+      <c r="E48" s="3">
         <v>295200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>100</v>
       </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
       <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
         <v>300</v>
       </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
       <c r="I48" s="3">
         <v>0</v>
       </c>
@@ -1796,39 +1903,45 @@
       <c r="K48" s="3">
         <v>0</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E49" s="3">
         <v>38200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>67900</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>5000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3300</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="K49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L49" s="3">
         <v>6700</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1856,9 +1969,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1886,27 +2002,30 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>400</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="E52" s="3">
+        <v>400</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>5</v>
       </c>
@@ -1916,9 +2035,12 @@
       <c r="K52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1946,39 +2068,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>398200</v>
+      </c>
+      <c r="E54" s="3">
         <v>431800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>85700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7600</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1991,8 +2119,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2005,142 +2134,155 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E57" s="3">
         <v>27500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E58" s="3">
         <v>19400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>400</v>
       </c>
       <c r="I58" s="3">
         <v>400</v>
       </c>
       <c r="J58" s="3">
+        <v>400</v>
+      </c>
+      <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>900</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E59" s="3">
         <v>7900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1300</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>58300</v>
+      </c>
+      <c r="E60" s="3">
         <v>54900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2900</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>240200</v>
+      </c>
+      <c r="E61" s="3">
         <v>226700</v>
-      </c>
-      <c r="E61" s="3">
-        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2152,41 +2294,47 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>2800</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E62" s="3">
         <v>29900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1800</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3">
         <v>400</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2214,9 +2362,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2244,9 +2395,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2274,39 +2428,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>336800</v>
+      </c>
+      <c r="E66" s="3">
         <v>335900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6100</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2319,8 +2479,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2348,9 +2509,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2378,9 +2542,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2408,9 +2575,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2438,39 +2608,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-409100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-363300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-31900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-18200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-12600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-12500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-9600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-10200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2800</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2498,9 +2674,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2528,9 +2707,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2558,39 +2740,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E76" s="3">
         <v>95900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>75100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-5900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1600</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2618,74 +2806,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-45800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-424800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>100</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2698,38 +2895,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E83" s="3">
         <v>13100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>500</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2757,9 +2958,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2787,9 +2991,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2817,9 +3024,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2847,9 +3057,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2877,39 +3090,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E89" s="3">
         <v>50600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2922,38 +3141,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14600</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2981,9 +3204,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3011,27 +3237,30 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>8000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
@@ -3041,9 +3270,12 @@
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3056,17 +3288,18 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E96" s="3">
         <v>-51200</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -3085,9 +3318,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3115,9 +3351,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3145,9 +3384,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3175,39 +3417,45 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-48100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>14000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3235,37 +3483,43 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>15300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NUTX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NUTX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
   <si>
     <t>NUTX</t>
   </si>
@@ -662,7 +662,9 @@
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -695,11 +697,11 @@
       <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
-        <v>43465</v>
-      </c>
-      <c r="J7" s="2">
-        <v>43100</v>
+      <c r="I7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="K7" s="2">
         <v>42735</v>
@@ -720,19 +722,19 @@
         <v>219300</v>
       </c>
       <c r="F8" s="3">
-        <v>18800</v>
+        <v>331500</v>
       </c>
       <c r="G8" s="3">
-        <v>1600</v>
+        <v>274000</v>
       </c>
       <c r="H8" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I8" s="3">
-        <v>100</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+        <v>97100</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -747,25 +749,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>212900</v>
+        <v>195300</v>
       </c>
       <c r="E9" s="3">
-        <v>205800</v>
+        <v>190700</v>
       </c>
       <c r="F9" s="3">
-        <v>14600</v>
+        <v>144600</v>
       </c>
       <c r="G9" s="3">
-        <v>900</v>
+        <v>104600</v>
       </c>
       <c r="H9" s="3">
-        <v>800</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0</v>
+        <v>40200</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -780,25 +782,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>34800</v>
+        <v>52400</v>
       </c>
       <c r="E10" s="3">
-        <v>13500</v>
+        <v>28600</v>
       </c>
       <c r="F10" s="3">
-        <v>4100</v>
+        <v>186900</v>
       </c>
       <c r="G10" s="3">
-        <v>700</v>
+        <v>169500</v>
       </c>
       <c r="H10" s="3">
-        <v>500</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
+        <v>56900</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -833,14 +835,14 @@
       <c r="E12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="3">
-        <v>300</v>
-      </c>
-      <c r="G12" s="3">
-        <v>600</v>
-      </c>
-      <c r="H12" s="3">
-        <v>800</v>
+      <c r="F12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>5</v>
@@ -900,19 +902,19 @@
         <v>402000</v>
       </c>
       <c r="F14" s="3">
-        <v>-600</v>
-      </c>
-      <c r="G14" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H14" s="3">
-        <v>2400</v>
-      </c>
-      <c r="I14" s="3">
-        <v>300</v>
-      </c>
-      <c r="J14" s="3">
-        <v>3400</v>
+        <v>-2000</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
@@ -926,26 +928,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>5</v>
+      <c r="D15" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E15" s="3">
+        <v>13100</v>
       </c>
       <c r="F15" s="3">
-        <v>700</v>
+        <v>7700</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>5900</v>
       </c>
       <c r="H15" s="3">
-        <v>200</v>
+        <v>2500</v>
       </c>
       <c r="I15" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>5</v>
@@ -972,25 +974,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>279400</v>
+        <v>248900</v>
       </c>
       <c r="E17" s="3">
-        <v>625900</v>
+        <v>223900</v>
       </c>
       <c r="F17" s="3">
-        <v>27200</v>
+        <v>157700</v>
       </c>
       <c r="G17" s="3">
-        <v>8800</v>
+        <v>120900</v>
       </c>
       <c r="H17" s="3">
-        <v>8400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J17" s="3">
-        <v>5800</v>
+        <v>62300</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K17" s="3">
         <v>400</v>
@@ -1005,25 +1007,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-31800</v>
+        <v>-1300</v>
       </c>
       <c r="E18" s="3">
-        <v>-406600</v>
+        <v>-4600</v>
       </c>
       <c r="F18" s="3">
-        <v>-8400</v>
+        <v>173800</v>
       </c>
       <c r="G18" s="3">
-        <v>-7200</v>
+        <v>153200</v>
       </c>
       <c r="H18" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-5800</v>
+        <v>34700</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K18" s="3">
         <v>-400</v>
@@ -1053,25 +1055,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-400</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
-        <v>-600</v>
+        <v>600</v>
       </c>
       <c r="F20" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>200</v>
+        <v>-900</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1086,25 +1088,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-14600</v>
+        <v>15900</v>
       </c>
       <c r="E21" s="3">
-        <v>-394000</v>
+        <v>8000</v>
       </c>
       <c r="F21" s="3">
-        <v>-7100</v>
+        <v>181400</v>
       </c>
       <c r="G21" s="3">
-        <v>-5200</v>
+        <v>158100</v>
       </c>
       <c r="H21" s="3">
-        <v>-6900</v>
+        <v>38100</v>
       </c>
       <c r="I21" s="3">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
-        <v>-5100</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>-400</v>
@@ -1125,19 +1127,19 @@
         <v>12500</v>
       </c>
       <c r="F22" s="3">
-        <v>6800</v>
+        <v>6200</v>
       </c>
       <c r="G22" s="3">
-        <v>300</v>
+        <v>6400</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>600</v>
-      </c>
-      <c r="J22" s="3">
-        <v>400</v>
+        <v>3500</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1158,19 +1160,19 @@
         <v>-419600</v>
       </c>
       <c r="F23" s="3">
-        <v>-14700</v>
+        <v>169500</v>
       </c>
       <c r="G23" s="3">
-        <v>-5700</v>
+        <v>145700</v>
       </c>
       <c r="H23" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-6000</v>
+        <v>32100</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K23" s="3">
         <v>-500</v>
@@ -1191,10 +1193,10 @@
         <v>13100</v>
       </c>
       <c r="F24" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>5</v>
+        <v>1000</v>
+      </c>
+      <c r="G24" s="3">
+        <v>200</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>5</v>
@@ -1257,19 +1259,19 @@
         <v>-432700</v>
       </c>
       <c r="F26" s="3">
-        <v>-13700</v>
+        <v>168500</v>
       </c>
       <c r="G26" s="3">
-        <v>-5700</v>
+        <v>145600</v>
       </c>
       <c r="H26" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-6000</v>
+        <v>32100</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K26" s="3">
         <v>-500</v>
@@ -1290,19 +1292,19 @@
         <v>-424800</v>
       </c>
       <c r="F27" s="3">
-        <v>-13700</v>
+        <v>132600</v>
       </c>
       <c r="G27" s="3">
-        <v>-5700</v>
+        <v>106000</v>
       </c>
       <c r="H27" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-6000</v>
+        <v>20900</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K27" s="3">
         <v>-500</v>
@@ -1349,11 +1351,11 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1361,14 +1363,14 @@
       <c r="G29" s="3">
         <v>0</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>-7000</v>
@@ -1449,25 +1451,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>400</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
-        <v>600</v>
+        <v>-600</v>
       </c>
       <c r="F32" s="3">
-        <v>-500</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>-1800</v>
+        <v>-1000</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-200</v>
+        <v>900</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1488,19 +1490,19 @@
         <v>-424800</v>
       </c>
       <c r="F33" s="3">
-        <v>-13700</v>
+        <v>132600</v>
       </c>
       <c r="G33" s="3">
-        <v>-5700</v>
+        <v>106000</v>
       </c>
       <c r="H33" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="J33" s="3">
-        <v>600</v>
+        <v>20900</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K33" s="3">
         <v>-7400</v>
@@ -1554,19 +1556,19 @@
         <v>-424800</v>
       </c>
       <c r="F35" s="3">
-        <v>-13700</v>
+        <v>132600</v>
       </c>
       <c r="G35" s="3">
-        <v>-5700</v>
+        <v>106000</v>
       </c>
       <c r="H35" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="J35" s="3">
-        <v>600</v>
+        <v>20900</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K35" s="3">
         <v>-7400</v>
@@ -1600,11 +1602,11 @@
       <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
-        <v>43465</v>
-      </c>
-      <c r="J38" s="2">
-        <v>43100</v>
+      <c r="I38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="K38" s="2">
         <v>42735</v>
@@ -1655,19 +1657,19 @@
         <v>34300</v>
       </c>
       <c r="F41" s="3">
-        <v>15300</v>
+        <v>36100</v>
       </c>
       <c r="G41" s="3">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="H41" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
+        <v>8000</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
@@ -1721,19 +1723,19 @@
         <v>58300</v>
       </c>
       <c r="F43" s="3">
-        <v>2100</v>
+        <v>114800</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>108100</v>
       </c>
       <c r="H43" s="3">
-        <v>100</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>36100</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -1753,17 +1755,17 @@
       <c r="E44" s="3">
         <v>3500</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>5</v>
+      <c r="F44" s="3">
+        <v>2800</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
+        <v>900</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
@@ -1780,26 +1782,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>2700</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>500</v>
@@ -1820,19 +1822,19 @@
         <v>98000</v>
       </c>
       <c r="F46" s="3">
-        <v>17700</v>
+        <v>154000</v>
       </c>
       <c r="G46" s="3">
-        <v>200</v>
+        <v>135500</v>
       </c>
       <c r="H46" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I46" s="3">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3">
-        <v>100</v>
+        <v>45700</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K46" s="3">
         <v>500</v>
@@ -1852,20 +1854,20 @@
       <c r="E47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -1886,19 +1888,19 @@
         <v>295200</v>
       </c>
       <c r="F48" s="3">
-        <v>100</v>
+        <v>238400</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
+        <v>170800</v>
       </c>
       <c r="H48" s="3">
-        <v>300</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+        <v>131300</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -1919,19 +1921,19 @@
         <v>38200</v>
       </c>
       <c r="F49" s="3">
-        <v>67900</v>
+        <v>1800</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H49" s="3">
-        <v>5000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J49" s="3">
-        <v>3300</v>
+        <v>1100</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>5</v>
@@ -2017,14 +2019,14 @@
       <c r="E52" s="3">
         <v>400</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
+      <c r="F52" s="3">
+        <v>500</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>5</v>
@@ -2084,19 +2086,19 @@
         <v>431800</v>
       </c>
       <c r="F54" s="3">
-        <v>85700</v>
+        <v>394700</v>
       </c>
       <c r="G54" s="3">
-        <v>200</v>
+        <v>308600</v>
       </c>
       <c r="H54" s="3">
-        <v>6700</v>
-      </c>
-      <c r="I54" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J54" s="3">
-        <v>3300</v>
+        <v>179200</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K54" s="3">
         <v>500</v>
@@ -2144,22 +2146,22 @@
         <v>25300</v>
       </c>
       <c r="E57" s="3">
-        <v>27500</v>
+        <v>23900</v>
       </c>
       <c r="F57" s="3">
-        <v>3500</v>
+        <v>17700</v>
       </c>
       <c r="G57" s="3">
-        <v>700</v>
+        <v>8600</v>
       </c>
       <c r="H57" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I57" s="3">
-        <v>500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>300</v>
+        <v>5300</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K57" s="3">
         <v>400</v>
@@ -2174,25 +2176,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>18500</v>
+        <v>20100</v>
       </c>
       <c r="E58" s="3">
-        <v>19400</v>
+        <v>21100</v>
       </c>
       <c r="F58" s="3">
-        <v>4600</v>
+        <v>13200</v>
       </c>
       <c r="G58" s="3">
-        <v>300</v>
+        <v>20400</v>
       </c>
       <c r="H58" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>400</v>
+        <v>63700</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
@@ -2206,26 +2208,26 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>14500</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E59" s="3">
-        <v>7900</v>
-      </c>
-      <c r="F59" s="3">
-        <v>500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>200</v>
+        <v>3500</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>6000</v>
@@ -2246,19 +2248,19 @@
         <v>54900</v>
       </c>
       <c r="F60" s="3">
-        <v>8600</v>
+        <v>37700</v>
       </c>
       <c r="G60" s="3">
-        <v>1200</v>
+        <v>31500</v>
       </c>
       <c r="H60" s="3">
-        <v>4600</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1000</v>
+        <v>72100</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K60" s="3">
         <v>6400</v>
@@ -2273,19 +2275,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>240200</v>
+        <v>255700</v>
       </c>
       <c r="E61" s="3">
-        <v>226700</v>
+        <v>246100</v>
       </c>
       <c r="F61" s="3">
-        <v>100</v>
+        <v>165400</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>129700</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>56300</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2305,20 +2307,20 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>20600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>29900</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>200</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>5</v>
@@ -2438,25 +2440,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>336800</v>
+        <v>319100</v>
       </c>
       <c r="E66" s="3">
-        <v>335900</v>
+        <v>311400</v>
       </c>
       <c r="F66" s="3">
-        <v>10600</v>
+        <v>203100</v>
       </c>
       <c r="G66" s="3">
-        <v>1300</v>
+        <v>161200</v>
       </c>
       <c r="H66" s="3">
-        <v>4800</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1000</v>
+        <v>128400</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K66" s="3">
         <v>6400</v>
@@ -2624,19 +2626,19 @@
         <v>-363300</v>
       </c>
       <c r="F72" s="3">
-        <v>-31900</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-18200</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-12600</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-12500</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-9600</v>
+        <v>102300</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K72" s="3">
         <v>-10200</v>
@@ -2756,19 +2758,19 @@
         <v>95900</v>
       </c>
       <c r="F76" s="3">
-        <v>75100</v>
+        <v>114700</v>
       </c>
       <c r="G76" s="3">
-        <v>-1100</v>
+        <v>85800</v>
       </c>
       <c r="H76" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J76" s="3">
-        <v>2400</v>
+        <v>28300</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K76" s="3">
         <v>-5900</v>
@@ -2835,11 +2837,11 @@
       <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
-        <v>43465</v>
-      </c>
-      <c r="J80" s="2">
-        <v>43100</v>
+      <c r="I80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="K80" s="2">
         <v>42735</v>
@@ -2860,19 +2862,19 @@
         <v>-424800</v>
       </c>
       <c r="F81" s="3">
-        <v>-13700</v>
+        <v>132600</v>
       </c>
       <c r="G81" s="3">
-        <v>-5700</v>
+        <v>106000</v>
       </c>
       <c r="H81" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="J81" s="3">
-        <v>600</v>
+        <v>20900</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K81" s="3">
         <v>-7400</v>
@@ -2902,25 +2904,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>17600</v>
+        <v>14800</v>
       </c>
       <c r="E83" s="3">
-        <v>13100</v>
+        <v>12000</v>
       </c>
       <c r="F83" s="3">
-        <v>700</v>
+        <v>7700</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>5900</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>500</v>
+        <v>2500</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3106,19 +3108,19 @@
         <v>50600</v>
       </c>
       <c r="F89" s="3">
-        <v>-6700</v>
+        <v>173400</v>
       </c>
       <c r="G89" s="3">
-        <v>-1500</v>
+        <v>86700</v>
       </c>
       <c r="H89" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-700</v>
+        <v>12100</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K89" s="3">
         <v>-300</v>
@@ -3153,14 +3155,14 @@
       <c r="E91" s="3">
         <v>-14600</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>5</v>
+      <c r="F91" s="3">
+        <v>-36900</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-61200</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>-32300</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>5</v>
@@ -3253,19 +3255,19 @@
         <v>-4300</v>
       </c>
       <c r="F94" s="3">
-        <v>8000</v>
+        <v>-37000</v>
       </c>
       <c r="G94" s="3">
-        <v>-100</v>
+        <v>-61200</v>
       </c>
       <c r="H94" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+        <v>-31200</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -3295,19 +3297,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-5200</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-51200</v>
+        <v>34400</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>111700</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>45600</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>18900</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -3433,19 +3435,19 @@
         <v>-48100</v>
       </c>
       <c r="F100" s="3">
-        <v>14000</v>
+        <v>-125900</v>
       </c>
       <c r="G100" s="3">
-        <v>500</v>
+        <v>-8000</v>
       </c>
       <c r="H100" s="3">
-        <v>5700</v>
-      </c>
-      <c r="I100" s="3">
-        <v>800</v>
-      </c>
-      <c r="J100" s="3">
-        <v>700</v>
+        <v>21700</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K100" s="3">
         <v>200</v>
@@ -3459,26 +3461,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3499,13 +3501,13 @@
         <v>-1900</v>
       </c>
       <c r="F102" s="3">
-        <v>15300</v>
+        <v>10600</v>
       </c>
       <c r="G102" s="3">
-        <v>-1000</v>
+        <v>17500</v>
       </c>
       <c r="H102" s="3">
-        <v>900</v>
+        <v>2600</v>
       </c>
       <c r="I102" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/NUTX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NUTX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
   <si>
     <t>NUTX</t>
   </si>
@@ -656,161 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>479900</v>
+      </c>
+      <c r="E8" s="3">
         <v>247600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>219300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>331500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>274000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>97100</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>500</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>264700</v>
+      </c>
+      <c r="E9" s="3">
         <v>195300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>190700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>144600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>104600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>40200</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>215200</v>
+      </c>
+      <c r="E10" s="3">
         <v>52400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>28600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>186900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>169500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>56900</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="3">
         <v>500</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,8 +836,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -856,9 +869,12 @@
       <c r="L12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -889,24 +905,27 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E14" s="3">
         <v>30500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>402000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-2000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
@@ -922,42 +941,48 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E15" s="3">
         <v>17600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2500</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -968,74 +993,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>342200</v>
+      </c>
+      <c r="E17" s="3">
         <v>248900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>223900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>157700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>120900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>62300</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1000</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>137700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>173800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>153200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>34700</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1049,158 +1081,171 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-900</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E21" s="3">
         <v>15900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>181400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>158100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>38100</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
         <v>0</v>
       </c>
       <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>-400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-500</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E22" s="3">
         <v>16300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3500</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>109700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-48500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-419600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>169500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>145700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>32100</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K23" s="3">
-        <v>-500</v>
+      <c r="K23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L23" s="3">
         <v>-500</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-5100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>5</v>
       </c>
@@ -1213,9 +1258,12 @@
       <c r="L24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1246,75 +1294,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-43400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-432700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>168500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>145600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>32100</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K26" s="3">
-        <v>-500</v>
+      <c r="K26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-45800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-424800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>132600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>106000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>20900</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K27" s="3">
-        <v>-500</v>
+      <c r="K27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1345,9 +1402,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1373,14 +1433,17 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-7000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>600</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1411,9 +1474,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1444,75 +1510,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>900</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-45800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-424800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>132600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>106000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>20900</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3">
         <v>-7400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>100</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1543,80 +1618,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-45800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-424800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>132600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>106000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>20900</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3">
         <v>-7400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>100</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K38" s="2">
+      <c r="K38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1630,8 +1714,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1645,41 +1730,45 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E41" s="3">
         <v>22000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>34300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8000</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
+      <c r="K41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1710,75 +1799,84 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>236100</v>
+      </c>
+      <c r="E43" s="3">
         <v>62800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>58300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>114800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>108100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>36100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>200</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E44" s="3">
         <v>3400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>900</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1803,48 +1901,54 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
-        <v>500</v>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3">
+        <v>500</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>292500</v>
+      </c>
+      <c r="E46" s="3">
         <v>90800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>98000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>154000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>135500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>45700</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L46" s="3">
         <v>500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>900</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1869,68 +1973,74 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>324700</v>
+      </c>
+      <c r="E48" s="3">
         <v>269400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>295200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>238400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>170800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>131300</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E49" s="3">
         <v>37600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>38200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1800</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1100</v>
       </c>
       <c r="H49" s="3">
         <v>1100</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
+      <c r="I49" s="3">
+        <v>1100</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
@@ -1938,12 +2048,15 @@
       <c r="K49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L49" s="3">
+      <c r="L49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M49" s="3">
         <v>6700</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1974,9 +2087,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2007,29 +2123,32 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E52" s="3">
         <v>400</v>
       </c>
       <c r="F52" s="3">
+        <v>400</v>
+      </c>
+      <c r="G52" s="3">
         <v>500</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1100</v>
       </c>
       <c r="H52" s="3">
         <v>1100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
+      <c r="I52" s="3">
+        <v>1100</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
@@ -2040,9 +2159,12 @@
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2073,42 +2195,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>655300</v>
+      </c>
+      <c r="E54" s="3">
         <v>398200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>431800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>394700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>308600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>179200</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L54" s="3">
         <v>500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7600</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2122,8 +2250,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2137,86 +2266,93 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>25300</v>
+        <v>10200</v>
       </c>
       <c r="E57" s="3">
+        <v>20100</v>
+      </c>
+      <c r="F57" s="3">
         <v>23900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5300</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E58" s="3">
         <v>20100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>21100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>63700</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>900</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
+      <c r="D59" s="3">
+        <v>77500</v>
       </c>
       <c r="E59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F59" s="3">
         <v>3500</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>5</v>
       </c>
@@ -2229,69 +2365,75 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>6000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1300</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>140900</v>
+      </c>
+      <c r="E60" s="3">
         <v>58300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>54900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>37700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>31500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>72100</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L60" s="3">
         <v>6400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2900</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>312600</v>
+      </c>
+      <c r="E61" s="3">
         <v>255700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>246100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>165400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>129700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>56300</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2299,11 +2441,14 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>2800</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2331,12 +2476,15 @@
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
         <v>400</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2367,9 +2515,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2400,9 +2551,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2433,42 +2587,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>453400</v>
+      </c>
+      <c r="E66" s="3">
         <v>319100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>311400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>203100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>161200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>128400</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L66" s="3">
         <v>6400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6100</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2482,8 +2642,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2514,9 +2675,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2547,9 +2711,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2580,9 +2747,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2613,24 +2783,27 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-356900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-409100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-363300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>102300</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>5</v>
       </c>
@@ -2640,15 +2813,18 @@
       <c r="J72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L72" s="3">
         <v>-10200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2800</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2679,9 +2855,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2712,9 +2891,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2745,42 +2927,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>146300</v>
+      </c>
+      <c r="E76" s="3">
         <v>61500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>95900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>114700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>85800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>28300</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L76" s="3">
         <v>-5900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1600</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2811,80 +2999,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K80" s="2">
+      <c r="K80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-45800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-424800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>132600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>106000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>20900</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3">
         <v>-7400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>100</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2898,41 +3095,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>14800</v>
+        <v>17500</v>
       </c>
       <c r="E83" s="3">
-        <v>12000</v>
+        <v>16000</v>
       </c>
       <c r="F83" s="3">
+        <v>11900</v>
+      </c>
+      <c r="G83" s="3">
         <v>7700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2500</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2963,9 +3164,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2996,9 +3200,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3029,9 +3236,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3062,9 +3272,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3095,42 +3308,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>50600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>173400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>86700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12100</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3144,41 +3363,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-36900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-61200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-32300</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3209,9 +3432,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3242,42 +3468,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-37000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-61200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31200</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3291,8 +3523,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3300,20 +3533,20 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>34400</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>16900</v>
+      </c>
+      <c r="G96" s="3">
         <v>111700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>45600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>18900</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -3323,9 +3556,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3356,9 +3592,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3389,9 +3628,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3422,42 +3664,48 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-48100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-125900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>21700</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3482,46 +3730,52 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>17500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2600</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NUTX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NUTX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
   <si>
     <t>NUTX</t>
   </si>
@@ -656,173 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>875300</v>
+      </c>
+      <c r="E8" s="3">
         <v>479900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>247600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>219300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>331500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>274000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>97100</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>500</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>264700</v>
+        <v>403900</v>
       </c>
       <c r="E9" s="3">
-        <v>195300</v>
+        <v>259100</v>
       </c>
       <c r="F9" s="3">
+        <v>189800</v>
+      </c>
+      <c r="G9" s="3">
         <v>190700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>144600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>104600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>40200</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>215200</v>
+        <v>471300</v>
       </c>
       <c r="E10" s="3">
-        <v>52400</v>
+        <v>220800</v>
       </c>
       <c r="F10" s="3">
+        <v>57900</v>
+      </c>
+      <c r="G10" s="3">
         <v>28600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>186900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>169500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>56900</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>500</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +849,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,9 +885,12 @@
       <c r="M12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -908,27 +924,30 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E14" s="3">
         <v>7100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>30500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>402000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
@@ -944,45 +963,51 @@
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E15" s="3">
         <v>19000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>17600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>13100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2500</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>5</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -994,80 +1019,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>482600</v>
+      </c>
+      <c r="E17" s="3">
         <v>342200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>248900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>223900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>157700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>120900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>62300</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>392600</v>
+      </c>
+      <c r="E18" s="3">
         <v>137800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>173800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>153200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>34700</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1082,173 +1114,186 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E20" s="3">
         <v>900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-900</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>404500</v>
+      </c>
+      <c r="E21" s="3">
         <v>155800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>15900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>181400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>158100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>38100</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
       <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
         <v>-400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-500</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E22" s="3">
         <v>19900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3500</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>244800</v>
+      </c>
+      <c r="E23" s="3">
         <v>109800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-48500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-419600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>169500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>145700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>32100</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L23" s="3">
-        <v>-500</v>
+      <c r="L23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M23" s="3">
         <v>-500</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E24" s="3">
         <v>15000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-5100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>5</v>
       </c>
@@ -1261,9 +1306,12 @@
       <c r="M24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1297,81 +1345,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>180400</v>
+      </c>
+      <c r="E26" s="3">
         <v>94800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-43400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-432700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>168500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>145600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>32100</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L26" s="3">
-        <v>-500</v>
+      <c r="L26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M26" s="3">
         <v>-500</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E27" s="3">
         <v>52100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-45800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-424800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>132600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>106000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20900</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L27" s="3">
-        <v>-500</v>
+      <c r="L27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1405,9 +1462,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1436,14 +1496,17 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-7000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>600</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1477,9 +1540,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1513,81 +1579,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>900</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E33" s="3">
         <v>52100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-45800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-424800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>132600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>106000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>20900</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3">
         <v>-7400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>100</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1621,86 +1696,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E35" s="3">
         <v>52100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-45800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-424800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>132600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>106000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>20900</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3">
         <v>-7400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>100</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L38" s="2">
+      <c r="L38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1715,8 +1799,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1731,44 +1816,48 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>185600</v>
+      </c>
+      <c r="E41" s="3">
         <v>40600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>34300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8000</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
+      <c r="L41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
         <v>100</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1802,90 +1891,99 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>325400</v>
+      </c>
+      <c r="E43" s="3">
         <v>236100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>62800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>58300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>114800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>108100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>36100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F44" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G44" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H44" s="3">
         <v>2800</v>
       </c>
-      <c r="E44" s="3">
-        <v>3400</v>
-      </c>
-      <c r="F44" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G44" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>900</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>2900</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
@@ -1904,51 +2002,57 @@
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
-        <v>500</v>
+      <c r="L45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>500</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>538800</v>
+      </c>
+      <c r="E46" s="3">
         <v>292500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>90800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>98000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>154000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>135500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>45700</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M46" s="3">
         <v>500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>900</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1976,74 +2080,80 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>343900</v>
+      </c>
+      <c r="E48" s="3">
         <v>324700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>269400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>295200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>238400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>170800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>131300</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E49" s="3">
         <v>29400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>37600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>38200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1800</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1100</v>
       </c>
       <c r="I49" s="3">
         <v>1100</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
+      <c r="J49" s="3">
+        <v>1100</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>5</v>
@@ -2051,12 +2161,15 @@
       <c r="L49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M49" s="3">
+      <c r="M49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N49" s="3">
         <v>6700</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2090,9 +2203,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2126,9 +2242,12 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2136,22 +2255,22 @@
         <v>700</v>
       </c>
       <c r="E52" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="F52" s="3">
         <v>400</v>
       </c>
       <c r="G52" s="3">
+        <v>400</v>
+      </c>
+      <c r="H52" s="3">
         <v>500</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1100</v>
       </c>
       <c r="I52" s="3">
         <v>1100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
+      <c r="J52" s="3">
+        <v>1100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
@@ -2162,9 +2281,12 @@
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2198,45 +2320,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>918500</v>
+      </c>
+      <c r="E54" s="3">
         <v>655300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>398200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>431800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>394700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>308600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>179200</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M54" s="3">
         <v>500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7600</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2251,8 +2379,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2267,95 +2396,102 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10400</v>
+        <v>45900</v>
       </c>
       <c r="E57" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F57" s="3">
         <v>20100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5300</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E58" s="3">
         <v>27700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>20100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>21100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>63700</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>900</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>74300</v>
+        <v>52600</v>
       </c>
       <c r="E59" s="3">
+        <v>75900</v>
+      </c>
+      <c r="F59" s="3">
         <v>4300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3500</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>5</v>
       </c>
@@ -2368,75 +2504,81 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>6000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1300</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>157900</v>
+      </c>
+      <c r="E60" s="3">
         <v>154200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>58300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>54900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>37700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>31500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>72100</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M60" s="3">
         <v>6400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2900</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>328100</v>
+      </c>
+      <c r="E61" s="3">
         <v>312600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>255700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>246100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>165400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>129700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>56300</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2444,11 +2586,14 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>2800</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2479,12 +2624,15 @@
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3">
         <v>400</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2518,9 +2666,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2554,9 +2705,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2590,45 +2744,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>495100</v>
+      </c>
+      <c r="E66" s="3">
         <v>466800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>319100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>311400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>203100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>161200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>128400</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M66" s="3">
         <v>6400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6100</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2643,8 +2803,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2678,9 +2839,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2714,9 +2878,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2750,9 +2917,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2786,27 +2956,30 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-286200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-357000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-409100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-363300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>102300</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>5</v>
       </c>
@@ -2816,15 +2989,18 @@
       <c r="K72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M72" s="3">
         <v>-10200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2800</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2858,9 +3034,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2894,9 +3073,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2930,45 +3112,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>329400</v>
+      </c>
+      <c r="E76" s="3">
         <v>132400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>61500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>95900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>114700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>85800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>28300</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M76" s="3">
         <v>-5900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1600</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3002,86 +3190,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L80" s="2">
+      <c r="L80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E81" s="3">
         <v>52100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-45800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-424800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>132600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>106000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>20900</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3">
         <v>-7400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>100</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3096,44 +3293,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E83" s="3">
         <v>17500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2500</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3167,9 +3368,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3203,9 +3407,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3239,9 +3446,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3275,9 +3485,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3311,45 +3524,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>248100</v>
+      </c>
+      <c r="E89" s="3">
         <v>23200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>50600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>173400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>86700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12100</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3364,44 +3583,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-36900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-61200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-32300</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3435,9 +3658,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3471,45 +3697,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-37000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-61200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-31200</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3524,8 +3756,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3536,20 +3769,20 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>34400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>111700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>45600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>18900</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -3559,9 +3792,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3595,9 +3831,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3631,9 +3870,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3667,45 +3909,51 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-97900</v>
+      </c>
+      <c r="E100" s="3">
         <v>1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-48100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-125900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>21700</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3733,49 +3981,55 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>144900</v>
+      </c>
+      <c r="E102" s="3">
         <v>18600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>17500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2600</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
